--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N56_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>76.82131477447645</v>
+        <v>12.48346365085242</v>
       </c>
       <c r="D2" t="n">
-        <v>12.29258823494604</v>
+        <v>1.997545588178731</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
